--- a/DesignTable/Data/Table/Tables/monster_master.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oh\Desktop\DesignGenerator\Data\Data_Export\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{776FB3A5-9CD3-4561-92D7-86407D5AEE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F127DB6-3781-4AF8-A44E-B1F2CECACC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="0" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{353F6C32-1A07-4A78-92E0-5EA8289CDA10}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{353F6C32-1A07-4A78-92E0-5EA8289CDA10}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="40">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mon_id</t>
   </si>
   <si>
@@ -163,6 +159,14 @@
   </si>
   <si>
     <t>mon_prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -220,7 +224,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -235,7 +243,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="monster_master">
         <xsd:complexType>
@@ -250,6 +258,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -275,7 +284,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="monster_master_맵" RootElement="monster_master" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="monster_master_맵" RootElement="monster_master" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -284,37 +293,37 @@
   <autoFilter ref="A1:K2" xr:uid="{B7C79B58-76E5-4903-BF96-018FD3007C11}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{07CEA2CD-7C9C-4639-BE7A-BA535074F304}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8240D787-81F7-440B-9724-9BC915817C25}" uniqueName="mon_name" name="mon_name">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_name" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_name" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{C0317B9C-C284-4184-AB65-F32EB3BAC987}" uniqueName="mon_atk" name="mon_atk">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_atk" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_atk" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{BD18BC95-7BDE-44AB-92A9-3C51E4675832}" uniqueName="mon_def" name="mon_def">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_def" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_def" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{E17CDE9E-B3B8-4FFD-B99C-F7E08F601929}" uniqueName="mon_hp" name="mon_hp">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_hp" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_hp" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{688F45D9-2BAB-4A8E-9018-8E0D5997DEA1}" uniqueName="mon_speed" name="mon_speed">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_speed" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_speed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{52F5EB19-A7EE-473C-B698-22B4266D91E6}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{2D5C2702-42D0-4C29-8829-7A0AEC7CE5BF}" uniqueName="mon_searchAngle" name="mon_searchAngle">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_searchAngle" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_searchAngle" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{54AD7853-968D-4A3C-A2BC-C4909359E621}" uniqueName="mon_searchRange" name="mon_searchRange">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_searchRange" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_searchRange" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{B3417410-0673-47FA-82E4-867BEC798C24}" uniqueName="mon_keppRange" name="mon_keppRange">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_keppRange" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_keppRange" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{1E02730D-E25C-4901-AE30-1AD4D7D6D616}" uniqueName="mon_prefab" name="mon_prefab">
-      <xmlColumnPr mapId="1" xpath="/monster_master/record/mon_prefab" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_prefab" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -322,35 +331,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A56B2A5-FBFD-4687-9AAE-8E930443C58F}" name="표1" displayName="표1" ref="A1:I12" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I12" xr:uid="{0A56B2A5-FBFD-4687-9AAE-8E930443C58F}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A56B2A5-FBFD-4687-9AAE-8E930443C58F}" name="표1" displayName="표1" ref="A1:J12" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J12" xr:uid="{0A56B2A5-FBFD-4687-9AAE-8E930443C58F}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{28D4DEC2-FCA1-45AB-A300-8D7433865EA5}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{D2A0A763-10CD-4EF5-BC3E-825B66D95B93}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{12CD9C6B-C9EF-4737-8D25-9CBABFE0C8EF}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9CD925C2-C6B5-4420-940D-D4055481ECDF}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{88DDFF2A-BC0E-465C-8105-31EBB40962D9}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{B47462FF-A948-4D85-A475-DB0108C78A05}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D6E32198-DAA2-4931-95A9-07252E170C00}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{50A00CD7-E2F5-4126-B35C-331FF7311375}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{1505599F-4AF9-4D92-9DF7-D1C1FC6BECBD}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/monster_master/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{1505599F-4AF9-4D92-9DF7-D1C1FC6BECBD}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{0829B18C-0031-4E86-B5A9-57CE5301E508}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -659,37 +671,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -716,10 +728,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63DA6DE8-9246-4F85-BC92-D3D4C93218F9}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,325 +757,361 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
         <v>1016</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="1">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
         <v>1016</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/monster_master.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F127DB6-3781-4AF8-A44E-B1F2CECACC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54FF4E96-C202-4D1D-A017-0AECCEA72777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{353F6C32-1A07-4A78-92E0-5EA8289CDA10}"/>
   </bookViews>
@@ -284,7 +284,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="monster_master_맵" RootElement="monster_master" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="monster_master_맵" RootElement="monster_master" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -293,37 +293,37 @@
   <autoFilter ref="A1:K2" xr:uid="{B7C79B58-76E5-4903-BF96-018FD3007C11}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{07CEA2CD-7C9C-4639-BE7A-BA535074F304}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8240D787-81F7-440B-9724-9BC915817C25}" uniqueName="mon_name" name="mon_name">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_name" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_name" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{C0317B9C-C284-4184-AB65-F32EB3BAC987}" uniqueName="mon_atk" name="mon_atk">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_atk" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_atk" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{BD18BC95-7BDE-44AB-92A9-3C51E4675832}" uniqueName="mon_def" name="mon_def">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_def" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_def" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{E17CDE9E-B3B8-4FFD-B99C-F7E08F601929}" uniqueName="mon_hp" name="mon_hp">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_hp" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_hp" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{688F45D9-2BAB-4A8E-9018-8E0D5997DEA1}" uniqueName="mon_speed" name="mon_speed">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_speed" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_speed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{52F5EB19-A7EE-473C-B698-22B4266D91E6}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{2D5C2702-42D0-4C29-8829-7A0AEC7CE5BF}" uniqueName="mon_searchAngle" name="mon_searchAngle">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_searchAngle" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_searchAngle" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{54AD7853-968D-4A3C-A2BC-C4909359E621}" uniqueName="mon_searchRange" name="mon_searchRange">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_searchRange" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_searchRange" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{B3417410-0673-47FA-82E4-867BEC798C24}" uniqueName="mon_keppRange" name="mon_keppRange">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_keppRange" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_keppRange" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{1E02730D-E25C-4901-AE30-1AD4D7D6D616}" uniqueName="mon_prefab" name="mon_prefab">
-      <xmlColumnPr mapId="4" xpath="/monster_master/record/mon_prefab" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_prefab" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -335,34 +335,34 @@
   <autoFilter ref="A1:J12" xr:uid="{0A56B2A5-FBFD-4687-9AAE-8E930443C58F}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{28D4DEC2-FCA1-45AB-A300-8D7433865EA5}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{D2A0A763-10CD-4EF5-BC3E-825B66D95B93}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{12CD9C6B-C9EF-4737-8D25-9CBABFE0C8EF}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9CD925C2-C6B5-4420-940D-D4055481ECDF}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{88DDFF2A-BC0E-465C-8105-31EBB40962D9}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{B47462FF-A948-4D85-A475-DB0108C78A05}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D6E32198-DAA2-4931-95A9-07252E170C00}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{50A00CD7-E2F5-4126-B35C-331FF7311375}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{1505599F-4AF9-4D92-9DF7-D1C1FC6BECBD}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{0829B18C-0031-4E86-B5A9-57CE5301E508}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/monster_master/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/monster_master.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54FF4E96-C202-4D1D-A017-0AECCEA72777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F7C3062-CC5D-4732-9BB9-ECE0300D5FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{353F6C32-1A07-4A78-92E0-5EA8289CDA10}"/>
   </bookViews>
@@ -284,7 +284,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="monster_master_맵" RootElement="monster_master" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="monster_master_맵" RootElement="monster_master" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -293,37 +293,37 @@
   <autoFilter ref="A1:K2" xr:uid="{B7C79B58-76E5-4903-BF96-018FD3007C11}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{07CEA2CD-7C9C-4639-BE7A-BA535074F304}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8240D787-81F7-440B-9724-9BC915817C25}" uniqueName="mon_name" name="mon_name">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_name" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_name" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{C0317B9C-C284-4184-AB65-F32EB3BAC987}" uniqueName="mon_atk" name="mon_atk">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_atk" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_atk" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{BD18BC95-7BDE-44AB-92A9-3C51E4675832}" uniqueName="mon_def" name="mon_def">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_def" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_def" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{E17CDE9E-B3B8-4FFD-B99C-F7E08F601929}" uniqueName="mon_hp" name="mon_hp">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_hp" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_hp" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{688F45D9-2BAB-4A8E-9018-8E0D5997DEA1}" uniqueName="mon_speed" name="mon_speed">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_speed" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_speed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{52F5EB19-A7EE-473C-B698-22B4266D91E6}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{2D5C2702-42D0-4C29-8829-7A0AEC7CE5BF}" uniqueName="mon_searchAngle" name="mon_searchAngle">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_searchAngle" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_searchAngle" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{54AD7853-968D-4A3C-A2BC-C4909359E621}" uniqueName="mon_searchRange" name="mon_searchRange">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_searchRange" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_searchRange" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{B3417410-0673-47FA-82E4-867BEC798C24}" uniqueName="mon_keppRange" name="mon_keppRange">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_keppRange" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_keppRange" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{1E02730D-E25C-4901-AE30-1AD4D7D6D616}" uniqueName="mon_prefab" name="mon_prefab">
-      <xmlColumnPr mapId="6" xpath="/monster_master/record/mon_prefab" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_prefab" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -335,34 +335,34 @@
   <autoFilter ref="A1:J12" xr:uid="{0A56B2A5-FBFD-4687-9AAE-8E930443C58F}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{28D4DEC2-FCA1-45AB-A300-8D7433865EA5}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{D2A0A763-10CD-4EF5-BC3E-825B66D95B93}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{12CD9C6B-C9EF-4737-8D25-9CBABFE0C8EF}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9CD925C2-C6B5-4420-940D-D4055481ECDF}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{88DDFF2A-BC0E-465C-8105-31EBB40962D9}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{B47462FF-A948-4D85-A475-DB0108C78A05}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D6E32198-DAA2-4931-95A9-07252E170C00}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{50A00CD7-E2F5-4126-B35C-331FF7311375}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{1505599F-4AF9-4D92-9DF7-D1C1FC6BECBD}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{0829B18C-0031-4E86-B5A9-57CE5301E508}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/monster_master/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/monster_master.xlsx
+++ b/DesignTable/Data/Table/Tables/monster_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F7C3062-CC5D-4732-9BB9-ECE0300D5FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F90B2C34-0EFC-4891-9D17-F9DBF79BF33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{353F6C32-1A07-4A78-92E0-5EA8289CDA10}"/>
   </bookViews>
@@ -284,7 +284,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="monster_master_맵" RootElement="monster_master" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="monster_master_맵" RootElement="monster_master" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -293,37 +293,37 @@
   <autoFilter ref="A1:K2" xr:uid="{B7C79B58-76E5-4903-BF96-018FD3007C11}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{07CEA2CD-7C9C-4639-BE7A-BA535074F304}" uniqueName="mon_id" name="mon_id">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8240D787-81F7-440B-9724-9BC915817C25}" uniqueName="mon_name" name="mon_name">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_name" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_name" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{C0317B9C-C284-4184-AB65-F32EB3BAC987}" uniqueName="mon_atk" name="mon_atk">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_atk" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_atk" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{BD18BC95-7BDE-44AB-92A9-3C51E4675832}" uniqueName="mon_def" name="mon_def">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_def" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_def" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{E17CDE9E-B3B8-4FFD-B99C-F7E08F601929}" uniqueName="mon_hp" name="mon_hp">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_hp" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_hp" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{688F45D9-2BAB-4A8E-9018-8E0D5997DEA1}" uniqueName="mon_speed" name="mon_speed">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_speed" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_speed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{52F5EB19-A7EE-473C-B698-22B4266D91E6}" uniqueName="mon_type" name="mon_type">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{2D5C2702-42D0-4C29-8829-7A0AEC7CE5BF}" uniqueName="mon_searchAngle" name="mon_searchAngle">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_searchAngle" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_searchAngle" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{54AD7853-968D-4A3C-A2BC-C4909359E621}" uniqueName="mon_searchRange" name="mon_searchRange">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_searchRange" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_searchRange" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{B3417410-0673-47FA-82E4-867BEC798C24}" uniqueName="mon_keppRange" name="mon_keppRange">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_keppRange" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_keppRange" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{1E02730D-E25C-4901-AE30-1AD4D7D6D616}" uniqueName="mon_prefab" name="mon_prefab">
-      <xmlColumnPr mapId="8" xpath="/monster_master/record/mon_prefab" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/record/mon_prefab" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -335,34 +335,34 @@
   <autoFilter ref="A1:J12" xr:uid="{0A56B2A5-FBFD-4687-9AAE-8E930443C58F}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{28D4DEC2-FCA1-45AB-A300-8D7433865EA5}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{D2A0A763-10CD-4EF5-BC3E-825B66D95B93}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{12CD9C6B-C9EF-4737-8D25-9CBABFE0C8EF}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9CD925C2-C6B5-4420-940D-D4055481ECDF}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{88DDFF2A-BC0E-465C-8105-31EBB40962D9}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{B47462FF-A948-4D85-A475-DB0108C78A05}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D6E32198-DAA2-4931-95A9-07252E170C00}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{50A00CD7-E2F5-4126-B35C-331FF7311375}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{1505599F-4AF9-4D92-9DF7-D1C1FC6BECBD}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{0829B18C-0031-4E86-B5A9-57CE5301E508}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/monster_master/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/monster_master/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
